--- a/restaurant_crawler/restaurant_data_台北_義式餐廳_20250918_183808_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_義式餐廳_20250918_183808_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD22769-833A-45C1-9614-D68AD5015EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A355F75-35A1-4980-8BB8-85A4ADC24681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="572">
   <si>
     <t>name</t>
   </si>
@@ -845,24 +845,6 @@
   </si>
   <si>
     <t>ChIJuyk2l4qpQjQRILRCQId5ZZA</t>
-  </si>
-  <si>
-    <t>茱莉金牛排餐酒館</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區浦城街26巷2號</t>
-  </si>
-  <si>
-    <t>02 2368 0986</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/LE-SAGE-%E8%8C%B1%E8%8E%89%E9%87%91%E7%89%9B%E6%8E%92%E9%A4%90%E9%A4%A8-113875963688652</t>
-  </si>
-  <si>
-    <t>ChIJ6SD9j1OpQjQR9PEGhor-D9c</t>
-  </si>
-  <si>
-    <t>sagebistrotpe@gmail.com</t>
   </si>
   <si>
     <t>BELLINI CAFFE 台北復興店</t>
@@ -2132,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43" customWidth="1"/>
@@ -2191,7 +2173,7 @@
       <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I2" t="s">
@@ -2220,7 +2202,7 @@
       <c r="G3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I3" t="s">
@@ -2249,7 +2231,7 @@
       <c r="G4" t="s">
         <v>46</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>47</v>
       </c>
       <c r="I4" t="s">
@@ -2278,7 +2260,7 @@
       <c r="G5" t="s">
         <v>57</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>58</v>
       </c>
       <c r="I5" t="s">
@@ -2307,7 +2289,7 @@
       <c r="G6" t="s">
         <v>73</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I6" t="s">
@@ -2336,7 +2318,7 @@
       <c r="G7" t="s">
         <v>104</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I7" t="s">
@@ -2365,7 +2347,7 @@
       <c r="G8" t="s">
         <v>110</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>111</v>
       </c>
       <c r="I8" t="s">
@@ -2394,7 +2376,7 @@
       <c r="G9" t="s">
         <v>130</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2" t="s">
         <v>131</v>
       </c>
       <c r="I9" t="s">
@@ -2423,7 +2405,7 @@
       <c r="G10" t="s">
         <v>154</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>155</v>
       </c>
       <c r="I10" t="s">
@@ -2452,7 +2434,7 @@
       <c r="G11" t="s">
         <v>160</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="2" t="s">
         <v>161</v>
       </c>
       <c r="I11" t="s">
@@ -2481,7 +2463,7 @@
       <c r="G12" t="s">
         <v>166</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="2" t="s">
         <v>167</v>
       </c>
       <c r="I12" t="s">
@@ -2510,7 +2492,7 @@
       <c r="G13" t="s">
         <v>181</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="2" t="s">
         <v>182</v>
       </c>
       <c r="I13" t="s">
@@ -2539,7 +2521,7 @@
       <c r="G14" t="s">
         <v>192</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="2" t="s">
         <v>193</v>
       </c>
       <c r="I14" t="s">
@@ -2568,7 +2550,7 @@
       <c r="G15" t="s">
         <v>202</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="2" t="s">
         <v>203</v>
       </c>
       <c r="I15" t="s">
@@ -2597,7 +2579,7 @@
       <c r="G16" t="s">
         <v>242</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="2" t="s">
         <v>243</v>
       </c>
       <c r="I16" t="s">
@@ -2626,7 +2608,7 @@
       <c r="G17" t="s">
         <v>248</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="2" t="s">
         <v>249</v>
       </c>
       <c r="I17" t="s">
@@ -2655,7 +2637,7 @@
       <c r="G18" t="s">
         <v>254</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="2" t="s">
         <v>255</v>
       </c>
       <c r="I18" t="s">
@@ -2676,10 +2658,10 @@
         <v>278</v>
       </c>
       <c r="E19">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F19">
-        <v>1779</v>
+        <v>2424</v>
       </c>
       <c r="G19" t="s">
         <v>279</v>
@@ -2693,28 +2675,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B20" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C20" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E20">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F20">
-        <v>2424</v>
+        <v>867</v>
       </c>
       <c r="G20" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="I20" t="s">
         <v>21</v>
@@ -2722,28 +2704,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C21" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D21" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E21">
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F21">
-        <v>867</v>
+        <v>4776</v>
       </c>
       <c r="G21" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I21" t="s">
         <v>21</v>
@@ -2751,28 +2733,28 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="B22" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C22" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="D22" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="E22">
-        <v>4.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="F22">
-        <v>4776</v>
+        <v>284</v>
       </c>
       <c r="G22" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="I22" t="s">
         <v>21</v>
@@ -2780,28 +2762,28 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="B23" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="C23" t="s">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="D23" t="s">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="E23">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F23">
-        <v>284</v>
+        <v>677</v>
       </c>
       <c r="G23" t="s">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
       <c r="I23" t="s">
         <v>21</v>
@@ -2809,28 +2791,28 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B24" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C24" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D24" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E24">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F24">
-        <v>677</v>
+        <v>2841</v>
       </c>
       <c r="G24" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I24" t="s">
         <v>21</v>
@@ -2838,28 +2820,28 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B25" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C25" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D25" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E25">
         <v>4.5</v>
       </c>
       <c r="F25">
-        <v>2841</v>
+        <v>1269</v>
       </c>
       <c r="G25" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="I25" t="s">
         <v>21</v>
@@ -2879,10 +2861,10 @@
         <v>401</v>
       </c>
       <c r="E26">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="F26">
-        <v>1269</v>
+        <v>2003</v>
       </c>
       <c r="G26" t="s">
         <v>402</v>
@@ -2908,10 +2890,10 @@
         <v>407</v>
       </c>
       <c r="E27">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F27">
-        <v>2003</v>
+        <v>2393</v>
       </c>
       <c r="G27" t="s">
         <v>408</v>
@@ -2925,28 +2907,28 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="B28" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="C28" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="D28" t="s">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="E28">
-        <v>4.0999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F28">
-        <v>2393</v>
+        <v>1443</v>
       </c>
       <c r="G28" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="I28" t="s">
         <v>21</v>
@@ -2954,28 +2936,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B29" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C29" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D29" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E29">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="F29">
-        <v>1443</v>
+        <v>3005</v>
       </c>
       <c r="G29" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="I29" t="s">
         <v>21</v>
@@ -2983,28 +2965,28 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B30" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="C30" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="D30" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="E30">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F30">
-        <v>3005</v>
+        <v>820</v>
       </c>
       <c r="G30" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="I30" t="s">
         <v>21</v>
@@ -3012,28 +2994,28 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="B31" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="C31" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="D31" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="E31">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F31">
-        <v>820</v>
+        <v>1453</v>
       </c>
       <c r="G31" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="I31" t="s">
         <v>21</v>
@@ -3041,28 +3023,25 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="B32" t="s">
-        <v>493</v>
-      </c>
-      <c r="C32" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D32" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E32">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F32">
-        <v>1453</v>
+        <v>682</v>
       </c>
       <c r="G32" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
@@ -3070,19 +3049,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>516</v>
+      </c>
+      <c r="B33" t="s">
         <v>517</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>518</v>
       </c>
       <c r="D33" t="s">
         <v>519</v>
       </c>
       <c r="E33">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F33">
-        <v>682</v>
+        <v>1729</v>
       </c>
       <c r="G33" t="s">
         <v>520</v>
@@ -3096,28 +3078,28 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="B34" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="C34" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="D34" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="E34">
         <v>4.4000000000000004</v>
       </c>
       <c r="F34">
-        <v>1729</v>
+        <v>3183</v>
       </c>
       <c r="G34" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="I34" t="s">
         <v>21</v>
@@ -3137,10 +3119,10 @@
         <v>541</v>
       </c>
       <c r="E35">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F35">
-        <v>3183</v>
+        <v>373</v>
       </c>
       <c r="G35" t="s">
         <v>542</v>
@@ -3154,28 +3136,28 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="B36" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="C36" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="D36" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="E36">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F36">
-        <v>373</v>
+        <v>2142</v>
       </c>
       <c r="G36" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="I36" t="s">
         <v>21</v>
@@ -3195,10 +3177,10 @@
         <v>563</v>
       </c>
       <c r="E37">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F37">
-        <v>2142</v>
+        <v>1370</v>
       </c>
       <c r="G37" t="s">
         <v>564</v>
@@ -3224,10 +3206,10 @@
         <v>569</v>
       </c>
       <c r="E38">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F38">
-        <v>1370</v>
+        <v>889</v>
       </c>
       <c r="G38" t="s">
         <v>570</v>
@@ -3239,56 +3221,50 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>572</v>
-      </c>
-      <c r="B39" t="s">
-        <v>573</v>
-      </c>
-      <c r="C39" t="s">
-        <v>574</v>
-      </c>
-      <c r="D39" t="s">
-        <v>575</v>
-      </c>
-      <c r="E39">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
         <v>4.5</v>
       </c>
-      <c r="F39">
-        <v>889</v>
-      </c>
-      <c r="G39" t="s">
-        <v>576</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="I39" t="s">
-        <v>21</v>
+      <c r="F47">
+        <v>2692</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E48">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F48">
-        <v>2692</v>
+        <v>5030</v>
       </c>
       <c r="G48" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I48" t="s">
         <v>14</v>
@@ -3296,22 +3272,25 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
       </c>
       <c r="E49">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F49">
-        <v>5030</v>
+        <v>4396</v>
       </c>
       <c r="G49" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I49" t="s">
         <v>14</v>
@@ -3319,25 +3298,25 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E50">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F50">
-        <v>4396</v>
+        <v>1004</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I50" t="s">
         <v>14</v>
@@ -3345,25 +3324,25 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E51">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F51">
-        <v>1004</v>
+        <v>1148</v>
       </c>
       <c r="G51" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I51" t="s">
         <v>14</v>
@@ -3371,25 +3350,25 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E52">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F52">
-        <v>1148</v>
+        <v>1612</v>
       </c>
       <c r="G52" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
         <v>14</v>
@@ -3397,25 +3376,25 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E53">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="F53">
-        <v>1612</v>
+        <v>3331</v>
       </c>
       <c r="G53" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I53" t="s">
         <v>14</v>
@@ -3423,25 +3402,25 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E54">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F54">
-        <v>3331</v>
+        <v>3820</v>
       </c>
       <c r="G54" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="I54" t="s">
         <v>14</v>
@@ -3449,25 +3428,25 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E55">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F55">
-        <v>3820</v>
+        <v>4285</v>
       </c>
       <c r="G55" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I55" t="s">
         <v>14</v>
@@ -3475,25 +3454,25 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B56" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D56" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E56">
-        <v>4.4000000000000004</v>
+        <v>4.7</v>
       </c>
       <c r="F56">
-        <v>4285</v>
+        <v>1117</v>
       </c>
       <c r="G56" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s">
         <v>14</v>
@@ -3501,25 +3480,25 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D57" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E57">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F57">
-        <v>1117</v>
+        <v>757</v>
       </c>
       <c r="G57" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I57" t="s">
         <v>14</v>
@@ -3527,25 +3506,25 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B58" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D58" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E58">
         <v>4.5999999999999996</v>
       </c>
       <c r="F58">
-        <v>757</v>
+        <v>5436</v>
       </c>
       <c r="G58" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I58" t="s">
         <v>14</v>
@@ -3553,25 +3532,25 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D59" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E59">
         <v>4.5999999999999996</v>
       </c>
       <c r="F59">
-        <v>5436</v>
+        <v>2366</v>
       </c>
       <c r="G59" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="I59" t="s">
         <v>14</v>
@@ -3579,25 +3558,25 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D60" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E60">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="F60">
-        <v>2366</v>
+        <v>1362</v>
       </c>
       <c r="G60" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I60" t="s">
         <v>14</v>
@@ -3605,25 +3584,22 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E61">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F61">
-        <v>1362</v>
+        <v>6983</v>
       </c>
       <c r="G61" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I61" t="s">
         <v>14</v>
@@ -3631,22 +3607,25 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>134</v>
+      </c>
+      <c r="D62" t="s">
+        <v>78</v>
       </c>
       <c r="E62">
         <v>4.5999999999999996</v>
       </c>
       <c r="F62">
-        <v>6983</v>
+        <v>4451</v>
       </c>
       <c r="G62" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I62" t="s">
         <v>14</v>
@@ -3654,25 +3633,22 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D63" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="E63">
         <v>4.5999999999999996</v>
       </c>
       <c r="F63">
-        <v>4451</v>
+        <v>747</v>
       </c>
       <c r="G63" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I63" t="s">
         <v>14</v>
@@ -3680,22 +3656,25 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>142</v>
+      </c>
+      <c r="D64" t="s">
+        <v>143</v>
       </c>
       <c r="E64">
-        <v>4.5999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="F64">
-        <v>747</v>
+        <v>2818</v>
       </c>
       <c r="G64" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I64" t="s">
         <v>14</v>
@@ -3703,25 +3682,25 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E65">
-        <v>4.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F65">
-        <v>2818</v>
+        <v>556</v>
       </c>
       <c r="G65" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I65" t="s">
         <v>14</v>
@@ -3729,25 +3708,25 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="D66" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="E66">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="F66">
-        <v>556</v>
+        <v>78</v>
       </c>
       <c r="G66" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="I66" t="s">
         <v>14</v>
@@ -3755,25 +3734,22 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B67" t="s">
-        <v>169</v>
-      </c>
-      <c r="C67" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E67">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F67">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G67" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I67" t="s">
         <v>14</v>
@@ -3781,22 +3757,25 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>184</v>
+      </c>
+      <c r="C68" t="s">
+        <v>185</v>
       </c>
       <c r="D68" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E68">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="F68">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="I68" t="s">
         <v>14</v>
@@ -3804,25 +3783,22 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B69" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C69" t="s">
-        <v>185</v>
-      </c>
-      <c r="D69" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E69">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F69">
-        <v>17</v>
+        <v>1936</v>
       </c>
       <c r="G69" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="I69" t="s">
         <v>14</v>
@@ -3830,22 +3806,25 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B70" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C70" t="s">
-        <v>196</v>
+        <v>206</v>
+      </c>
+      <c r="D70" t="s">
+        <v>207</v>
       </c>
       <c r="E70">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="F70">
-        <v>1936</v>
+        <v>1971</v>
       </c>
       <c r="G70" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="I70" t="s">
         <v>14</v>
@@ -3853,25 +3832,22 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B71" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C71" t="s">
-        <v>206</v>
-      </c>
-      <c r="D71" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E71">
         <v>4.7</v>
       </c>
       <c r="F71">
-        <v>1971</v>
+        <v>579</v>
       </c>
       <c r="G71" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="I71" t="s">
         <v>14</v>
@@ -3879,22 +3855,25 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B72" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C72" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="D72" t="s">
+        <v>216</v>
       </c>
       <c r="E72">
-        <v>4.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F72">
-        <v>579</v>
+        <v>1147</v>
       </c>
       <c r="G72" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I72" t="s">
         <v>14</v>
@@ -3902,25 +3881,25 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B73" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C73" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D73" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E73">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="F73">
-        <v>1147</v>
+        <v>734</v>
       </c>
       <c r="G73" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I73" t="s">
         <v>14</v>
@@ -3928,25 +3907,25 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D74" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="F74">
-        <v>734</v>
+        <v>500</v>
       </c>
       <c r="G74" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I74" t="s">
         <v>14</v>
@@ -3954,25 +3933,25 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B75" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C75" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D75" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E75">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F75">
-        <v>500</v>
+        <v>675</v>
       </c>
       <c r="G75" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I75" t="s">
         <v>14</v>
@@ -3980,25 +3959,25 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B76" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C76" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D76" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E76">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F76">
-        <v>675</v>
+        <v>1140</v>
       </c>
       <c r="G76" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I76" t="s">
         <v>14</v>
@@ -4006,25 +3985,22 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="B77" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C77" t="s">
-        <v>235</v>
-      </c>
-      <c r="D77" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="E77">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="F77">
-        <v>1140</v>
+        <v>43</v>
       </c>
       <c r="G77" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="I77" t="s">
         <v>14</v>
@@ -4032,22 +4008,25 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B78" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C78" t="s">
-        <v>258</v>
+        <v>262</v>
+      </c>
+      <c r="D78" t="s">
+        <v>263</v>
       </c>
       <c r="E78">
-        <v>4.8</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F78">
-        <v>43</v>
+        <v>1129</v>
       </c>
       <c r="G78" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I78" t="s">
         <v>14</v>
@@ -4055,25 +4034,25 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B79" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C79" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D79" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E79">
         <v>4.4000000000000004</v>
       </c>
       <c r="F79">
-        <v>1129</v>
+        <v>950</v>
       </c>
       <c r="G79" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I79" t="s">
         <v>14</v>
@@ -4081,25 +4060,25 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B80" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D80" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E80">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F80">
-        <v>950</v>
+        <v>3342</v>
       </c>
       <c r="G80" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I80" t="s">
         <v>14</v>
@@ -4107,25 +4086,25 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B81" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C81" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="D81" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E81">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F81">
-        <v>3342</v>
+        <v>4163</v>
       </c>
       <c r="G81" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I81" t="s">
         <v>14</v>
@@ -4133,25 +4112,25 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>286</v>
+      </c>
+      <c r="B82" t="s">
         <v>287</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>288</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>289</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F82">
+        <v>2727</v>
+      </c>
+      <c r="G82" t="s">
         <v>290</v>
-      </c>
-      <c r="E82">
-        <v>4.5</v>
-      </c>
-      <c r="F82">
-        <v>4163</v>
-      </c>
-      <c r="G82" t="s">
-        <v>291</v>
       </c>
       <c r="I82" t="s">
         <v>14</v>
@@ -4159,25 +4138,22 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B83" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C83" t="s">
-        <v>294</v>
-      </c>
-      <c r="D83" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E83">
         <v>4.4000000000000004</v>
       </c>
       <c r="F83">
-        <v>2727</v>
+        <v>1168</v>
       </c>
       <c r="G83" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I83" t="s">
         <v>14</v>
@@ -4185,22 +4161,25 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C84" t="s">
-        <v>305</v>
+        <v>309</v>
+      </c>
+      <c r="D84" t="s">
+        <v>310</v>
       </c>
       <c r="E84">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F84">
-        <v>1168</v>
+        <v>1430</v>
       </c>
       <c r="G84" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="I84" t="s">
         <v>14</v>
@@ -4208,25 +4187,25 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>312</v>
+      </c>
+      <c r="B85" t="s">
         <v>313</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>314</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>315</v>
-      </c>
-      <c r="D85" t="s">
-        <v>316</v>
       </c>
       <c r="E85">
         <v>4.5999999999999996</v>
       </c>
       <c r="F85">
-        <v>1430</v>
+        <v>732</v>
       </c>
       <c r="G85" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I85" t="s">
         <v>14</v>
@@ -4234,25 +4213,25 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>317</v>
+      </c>
+      <c r="B86" t="s">
         <v>318</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>319</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>320</v>
-      </c>
-      <c r="D86" t="s">
-        <v>321</v>
       </c>
       <c r="E86">
         <v>4.5999999999999996</v>
       </c>
       <c r="F86">
-        <v>732</v>
+        <v>431</v>
       </c>
       <c r="G86" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I86" t="s">
         <v>14</v>
@@ -4260,25 +4239,25 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C87" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D87" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E87">
-        <v>4.5999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="F87">
-        <v>431</v>
+        <v>363</v>
       </c>
       <c r="G87" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I87" t="s">
         <v>14</v>
@@ -4286,25 +4265,25 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>333</v>
+      </c>
+      <c r="B88" t="s">
         <v>334</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>335</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>336</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F88">
+        <v>1686</v>
+      </c>
+      <c r="G88" t="s">
         <v>337</v>
-      </c>
-      <c r="E88">
-        <v>4.3</v>
-      </c>
-      <c r="F88">
-        <v>363</v>
-      </c>
-      <c r="G88" t="s">
-        <v>338</v>
       </c>
       <c r="I88" t="s">
         <v>14</v>
@@ -4312,25 +4291,25 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>338</v>
+      </c>
+      <c r="B89" t="s">
         <v>339</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>340</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>341</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89">
+        <v>4.8</v>
+      </c>
+      <c r="F89">
+        <v>2982</v>
+      </c>
+      <c r="G89" t="s">
         <v>342</v>
-      </c>
-      <c r="E89">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F89">
-        <v>1686</v>
-      </c>
-      <c r="G89" t="s">
-        <v>343</v>
       </c>
       <c r="I89" t="s">
         <v>14</v>
@@ -4338,25 +4317,25 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>343</v>
+      </c>
+      <c r="B90" t="s">
         <v>344</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>345</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>346</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90">
+        <v>4.3</v>
+      </c>
+      <c r="F90">
+        <v>8750</v>
+      </c>
+      <c r="G90" t="s">
         <v>347</v>
-      </c>
-      <c r="E90">
-        <v>4.8</v>
-      </c>
-      <c r="F90">
-        <v>2982</v>
-      </c>
-      <c r="G90" t="s">
-        <v>348</v>
       </c>
       <c r="I90" t="s">
         <v>14</v>
@@ -4364,25 +4343,25 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>348</v>
+      </c>
+      <c r="B91" t="s">
         <v>349</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>350</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>351</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91">
+        <v>4.5</v>
+      </c>
+      <c r="F91">
+        <v>1320</v>
+      </c>
+      <c r="G91" t="s">
         <v>352</v>
-      </c>
-      <c r="E91">
-        <v>4.3</v>
-      </c>
-      <c r="F91">
-        <v>8750</v>
-      </c>
-      <c r="G91" t="s">
-        <v>353</v>
       </c>
       <c r="I91" t="s">
         <v>14</v>
@@ -4390,25 +4369,22 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>353</v>
+      </c>
+      <c r="B92" t="s">
         <v>354</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>355</v>
       </c>
-      <c r="C92" t="s">
+      <c r="E92">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F92">
+        <v>299</v>
+      </c>
+      <c r="G92" t="s">
         <v>356</v>
-      </c>
-      <c r="D92" t="s">
-        <v>357</v>
-      </c>
-      <c r="E92">
-        <v>4.5</v>
-      </c>
-      <c r="F92">
-        <v>1320</v>
-      </c>
-      <c r="G92" t="s">
-        <v>358</v>
       </c>
       <c r="I92" t="s">
         <v>14</v>
@@ -4416,22 +4392,25 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
+        <v>357</v>
+      </c>
+      <c r="B93" t="s">
+        <v>358</v>
+      </c>
+      <c r="C93" t="s">
         <v>359</v>
       </c>
-      <c r="B93" t="s">
+      <c r="D93" t="s">
+        <v>143</v>
+      </c>
+      <c r="E93">
+        <v>4.3</v>
+      </c>
+      <c r="F93">
+        <v>1921</v>
+      </c>
+      <c r="G93" t="s">
         <v>360</v>
-      </c>
-      <c r="C93" t="s">
-        <v>361</v>
-      </c>
-      <c r="E93">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F93">
-        <v>299</v>
-      </c>
-      <c r="G93" t="s">
-        <v>362</v>
       </c>
       <c r="I93" t="s">
         <v>14</v>
@@ -4439,25 +4418,25 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>361</v>
+      </c>
+      <c r="B94" t="s">
+        <v>362</v>
+      </c>
+      <c r="C94" t="s">
         <v>363</v>
       </c>
-      <c r="B94" t="s">
+      <c r="D94" t="s">
         <v>364</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94">
+        <v>4.5</v>
+      </c>
+      <c r="F94">
+        <v>740</v>
+      </c>
+      <c r="G94" t="s">
         <v>365</v>
-      </c>
-      <c r="D94" t="s">
-        <v>143</v>
-      </c>
-      <c r="E94">
-        <v>4.3</v>
-      </c>
-      <c r="F94">
-        <v>1921</v>
-      </c>
-      <c r="G94" t="s">
-        <v>366</v>
       </c>
       <c r="I94" t="s">
         <v>14</v>
@@ -4465,25 +4444,25 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>366</v>
+      </c>
+      <c r="B95" t="s">
         <v>367</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>368</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>369</v>
-      </c>
-      <c r="D95" t="s">
-        <v>370</v>
       </c>
       <c r="E95">
         <v>4.5</v>
       </c>
       <c r="F95">
-        <v>740</v>
+        <v>222</v>
       </c>
       <c r="G95" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I95" t="s">
         <v>14</v>
@@ -4491,25 +4470,22 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B96" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C96" t="s">
-        <v>374</v>
-      </c>
-      <c r="D96" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E96">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F96">
-        <v>222</v>
+        <v>1339</v>
       </c>
       <c r="G96" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I96" t="s">
         <v>14</v>
@@ -4517,22 +4493,25 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B97" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C97" t="s">
-        <v>385</v>
+        <v>389</v>
+      </c>
+      <c r="D97" t="s">
+        <v>390</v>
       </c>
       <c r="E97">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="F97">
-        <v>1339</v>
+        <v>219</v>
       </c>
       <c r="G97" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I97" t="s">
         <v>14</v>
@@ -4540,25 +4519,25 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="B98" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="C98" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="D98" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="E98">
-        <v>4.7</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F98">
-        <v>219</v>
+        <v>5459</v>
       </c>
       <c r="G98" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="I98" t="s">
         <v>14</v>
@@ -4566,25 +4545,25 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>415</v>
+      </c>
+      <c r="B99" t="s">
         <v>416</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>417</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>418</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F99">
+        <v>2745</v>
+      </c>
+      <c r="G99" t="s">
         <v>419</v>
-      </c>
-      <c r="E99">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="F99">
-        <v>5459</v>
-      </c>
-      <c r="G99" t="s">
-        <v>420</v>
       </c>
       <c r="I99" t="s">
         <v>14</v>
@@ -4592,25 +4571,25 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>420</v>
+      </c>
+      <c r="B100" t="s">
         <v>421</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>422</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>423</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100">
+        <v>4.8</v>
+      </c>
+      <c r="F100">
+        <v>2608</v>
+      </c>
+      <c r="G100" t="s">
         <v>424</v>
-      </c>
-      <c r="E100">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F100">
-        <v>2745</v>
-      </c>
-      <c r="G100" t="s">
-        <v>425</v>
       </c>
       <c r="I100" t="s">
         <v>14</v>
@@ -4618,25 +4597,25 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>425</v>
+      </c>
+      <c r="B101" t="s">
         <v>426</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>427</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>428</v>
-      </c>
-      <c r="D101" t="s">
-        <v>429</v>
       </c>
       <c r="E101">
         <v>4.8</v>
       </c>
       <c r="F101">
-        <v>2608</v>
+        <v>1884</v>
       </c>
       <c r="G101" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I101" t="s">
         <v>14</v>
@@ -4644,25 +4623,22 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
+        <v>430</v>
+      </c>
+      <c r="B102" t="s">
         <v>431</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>432</v>
       </c>
-      <c r="C102" t="s">
+      <c r="E102">
+        <v>4.5</v>
+      </c>
+      <c r="F102">
+        <v>1985</v>
+      </c>
+      <c r="G102" t="s">
         <v>433</v>
-      </c>
-      <c r="D102" t="s">
-        <v>434</v>
-      </c>
-      <c r="E102">
-        <v>4.8</v>
-      </c>
-      <c r="F102">
-        <v>1884</v>
-      </c>
-      <c r="G102" t="s">
-        <v>435</v>
       </c>
       <c r="I102" t="s">
         <v>14</v>
@@ -4670,22 +4646,25 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>434</v>
+      </c>
+      <c r="B103" t="s">
+        <v>435</v>
+      </c>
+      <c r="C103" t="s">
         <v>436</v>
       </c>
-      <c r="B103" t="s">
+      <c r="D103" t="s">
         <v>437</v>
-      </c>
-      <c r="C103" t="s">
-        <v>438</v>
       </c>
       <c r="E103">
         <v>4.5</v>
       </c>
       <c r="F103">
-        <v>1985</v>
+        <v>677</v>
       </c>
       <c r="G103" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I103" t="s">
         <v>14</v>
@@ -4693,25 +4672,25 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B104" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C104" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D104" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E104">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F104">
-        <v>677</v>
+        <v>2734</v>
       </c>
       <c r="G104" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="I104" t="s">
         <v>14</v>
@@ -4719,25 +4698,25 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B105" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C105" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D105" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E105">
         <v>4.5999999999999996</v>
       </c>
       <c r="F105">
-        <v>2734</v>
+        <v>588</v>
       </c>
       <c r="G105" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I105" t="s">
         <v>14</v>
@@ -4745,25 +4724,25 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>461</v>
+      </c>
+      <c r="B106" t="s">
         <v>462</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
         <v>463</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>464</v>
-      </c>
-      <c r="D106" t="s">
-        <v>465</v>
       </c>
       <c r="E106">
         <v>4.5999999999999996</v>
       </c>
       <c r="F106">
-        <v>588</v>
+        <v>3563</v>
       </c>
       <c r="G106" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I106" t="s">
         <v>14</v>
@@ -4771,25 +4750,25 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B107" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C107" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D107" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E107">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="F107">
-        <v>3563</v>
+        <v>3671</v>
       </c>
       <c r="G107" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="I107" t="s">
         <v>14</v>
@@ -4797,25 +4776,25 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>477</v>
+      </c>
+      <c r="B108" t="s">
         <v>478</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>479</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>480</v>
-      </c>
-      <c r="D108" t="s">
-        <v>481</v>
       </c>
       <c r="E108">
         <v>4.7</v>
       </c>
       <c r="F108">
-        <v>3671</v>
+        <v>1432</v>
       </c>
       <c r="G108" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I108" t="s">
         <v>14</v>
@@ -4823,25 +4802,25 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>482</v>
+      </c>
+      <c r="B109" t="s">
         <v>483</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>484</v>
       </c>
-      <c r="C109" t="s">
-        <v>485</v>
-      </c>
       <c r="D109" t="s">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="E109">
         <v>4.7</v>
       </c>
       <c r="F109">
-        <v>1432</v>
+        <v>3645</v>
       </c>
       <c r="G109" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I109" t="s">
         <v>14</v>
@@ -4849,25 +4828,22 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B110" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C110" t="s">
-        <v>490</v>
-      </c>
-      <c r="D110" t="s">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="E110">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="F110">
-        <v>3645</v>
+        <v>797</v>
       </c>
       <c r="G110" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="I110" t="s">
         <v>14</v>
@@ -4875,22 +4851,25 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>496</v>
+      </c>
+      <c r="B111" t="s">
+        <v>497</v>
+      </c>
+      <c r="C111" t="s">
         <v>498</v>
       </c>
-      <c r="B111" t="s">
+      <c r="D111" t="s">
         <v>499</v>
       </c>
-      <c r="C111" t="s">
+      <c r="E111">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F111">
+        <v>302</v>
+      </c>
+      <c r="G111" t="s">
         <v>500</v>
-      </c>
-      <c r="E111">
-        <v>4.3</v>
-      </c>
-      <c r="F111">
-        <v>797</v>
-      </c>
-      <c r="G111" t="s">
-        <v>501</v>
       </c>
       <c r="I111" t="s">
         <v>14</v>
@@ -4898,25 +4877,25 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>501</v>
+      </c>
+      <c r="B112" t="s">
         <v>502</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>503</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>504</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112">
+        <v>4.2</v>
+      </c>
+      <c r="F112">
+        <v>1131</v>
+      </c>
+      <c r="G112" t="s">
         <v>505</v>
-      </c>
-      <c r="E112">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F112">
-        <v>302</v>
-      </c>
-      <c r="G112" t="s">
-        <v>506</v>
       </c>
       <c r="I112" t="s">
         <v>14</v>
@@ -4924,25 +4903,25 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>506</v>
+      </c>
+      <c r="B113" t="s">
         <v>507</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>508</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>509</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113">
+        <v>4</v>
+      </c>
+      <c r="F113">
+        <v>995</v>
+      </c>
+      <c r="G113" t="s">
         <v>510</v>
-      </c>
-      <c r="E113">
-        <v>4.2</v>
-      </c>
-      <c r="F113">
-        <v>1131</v>
-      </c>
-      <c r="G113" t="s">
-        <v>511</v>
       </c>
       <c r="I113" t="s">
         <v>14</v>
@@ -4950,25 +4929,25 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="B114" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C114" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="D114" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="E114">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="F114">
-        <v>995</v>
+        <v>1046</v>
       </c>
       <c r="G114" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="I114" t="s">
         <v>14</v>
@@ -4976,25 +4955,25 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>527</v>
+      </c>
+      <c r="B115" t="s">
         <v>528</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>529</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>530</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F115">
+        <v>233</v>
+      </c>
+      <c r="G115" t="s">
         <v>531</v>
-      </c>
-      <c r="E115">
-        <v>4.3</v>
-      </c>
-      <c r="F115">
-        <v>1046</v>
-      </c>
-      <c r="G115" t="s">
-        <v>532</v>
       </c>
       <c r="I115" t="s">
         <v>14</v>
@@ -5002,25 +4981,25 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B116" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="C116" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="D116" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="E116">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="F116">
-        <v>233</v>
+        <v>10695</v>
       </c>
       <c r="G116" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="I116" t="s">
         <v>14</v>
@@ -5028,61 +5007,36 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>549</v>
+      </c>
+      <c r="B117" t="s">
         <v>550</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>551</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>552</v>
-      </c>
-      <c r="D117" t="s">
-        <v>553</v>
       </c>
       <c r="E117">
         <v>4.7</v>
       </c>
       <c r="F117">
-        <v>10695</v>
+        <v>169</v>
       </c>
       <c r="G117" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I117" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>555</v>
-      </c>
-      <c r="B118" t="s">
-        <v>556</v>
-      </c>
-      <c r="C118" t="s">
-        <v>557</v>
-      </c>
-      <c r="D118" t="s">
-        <v>558</v>
-      </c>
-      <c r="E118">
-        <v>4.7</v>
-      </c>
-      <c r="F118">
-        <v>169</v>
-      </c>
-      <c r="G118" t="s">
-        <v>559</v>
-      </c>
-      <c r="I118" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I118">
-    <sortCondition ref="I2:I118"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I117">
+    <sortCondition ref="I2:I117"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>